--- a/1.xlsx
+++ b/1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaimin\Desktop\mtry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7C35EF-A91F-4F0F-AFB3-EAAAA45EEEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005DD22D-7F0F-46D6-A381-F8DE99F7E2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,11 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="EUCInsightNameRange">Sheet2!$C$6</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,27 +31,12 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Version 8.2</t>
-  </si>
-  <si>
-    <t>Version 8.3</t>
-  </si>
-  <si>
-    <t>Version 9</t>
-  </si>
-  <si>
-    <t>GD Test</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -369,188 +350,54 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C25F4413-57FD-4D2B-B9EC-7AB66FCC0A40}">
-  <we:reference id="f3c9a2b1-7d4e-4a8f-9c2e-1b6f0a9d3c57" version="1.0.0.0" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences/>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{854B6C0C-49F4-4090-8117-5D647733C49C}">
-  <we:reference id="88f9deaa-1709-4aaa-bce8-0fb9f4c21c06" version="1.0.0.3" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences/>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A6A3A63-3061-4D2E-B85C-9845E337437D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A66AC0-7CCB-4008-98C5-DCC7F9F2EEE9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF6410E-A297-48F2-8490-6FFAEB446CBF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE270D96-5F57-4BD7-9A36-DD0DF5A38179}">
+  <dimension ref="F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <f>45*9</f>
-        <v>405</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D49ECA8A-32AD-409F-ADE9-7854225F6C00}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="D5:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5CCFBF-1CD8-4758-827A-77231DF2414B}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K6">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E9">
-        <f>4*5</f>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f>20</f>
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B400B6E-A6D1-47E6-B636-B38472AE2EAD}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="D3:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D3">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="K5">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="6" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G6">
-        <f>1*32</f>
-        <v>32</v>
-      </c>
-      <c r="I6">
-        <f>45*6532</f>
-        <v>293940</v>
-      </c>
-      <c r="K6">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="7" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="K7">
-        <f>SUM(K5:K6)</f>
-        <v>780</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8370135A-FEA5-4137-A022-6996DCD692E5}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5435</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <f>SUM(A1:A3)</f>
-        <v>5813</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8B67BC-AC64-459C-9638-525D13C8A854}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="I14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="14" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>